--- a/2. Components/2.1. Cloud Component/2.1.1. Autonomous_Database (wip)/3. autonomous_db_owner (wip)/4. dml/3. user_area [18-20,29-35,10]/18. role.xlsx
+++ b/2. Components/2.1. Cloud Component/2.1.1. Autonomous_Database (wip)/3. autonomous_db_owner (wip)/4. dml/3. user_area [18-20,29-35,10]/18. role.xlsx
@@ -5,18 +5,18 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github_projects\Tech_Hunt_Engine\2. Components\2.1. Cloud Component\2.1.1. Autonomous_Database\3. autonomous_db_owner (wip)\4. dml\3. user_area [18-20,29-35,10]\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github_projects\Tech_Hunt_Engine\2. Components\2.1. Cloud Component\2.1.1. Autonomous_Database (wip)\3. autonomous_db_owner (wip)\4. dml\3. user_area [18-20,29-35,10]\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E64FED43-AB38-4FDC-8505-0A0944883800}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86BBB2A8-5681-4876-93D0-C148DE9C11C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1515" yWindow="1515" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="role_table" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">role_table!$A$1:$A$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">role_table!$A$1:$A$3</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
@@ -28,16 +28,16 @@
     <t>name</t>
   </si>
   <si>
-    <t>admin</t>
-  </si>
-  <si>
-    <t>student</t>
-  </si>
-  <si>
-    <t>specialist_HR</t>
-  </si>
-  <si>
-    <t>manager</t>
+    <t>ADMIN</t>
+  </si>
+  <si>
+    <t>SPECIALIST_HR</t>
+  </si>
+  <si>
+    <t>MANAGER</t>
+  </si>
+  <si>
+    <t>STUDENT</t>
   </si>
 </sst>
 </file>
@@ -106,13 +106,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -337,29 +336,29 @@
     <col min="1" max="1" width="25.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="3" t="s">
-        <v>4</v>
+      <c r="A5" s="2" t="s">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
